--- a/engine/publish_queue/TMGH/TMGH_Valuation_Model_10092026.xlsx
+++ b/engine/publish_queue/TMGH/TMGH_Valuation_Model_10092026.xlsx
@@ -2295,7 +2295,7 @@
         </is>
       </c>
       <c r="B7" s="13" t="n">
-        <v>0.3710320302096666</v>
+        <v>0.3256539205036353</v>
       </c>
     </row>
     <row r="8">
@@ -2305,7 +2305,7 @@
         </is>
       </c>
       <c r="B8" s="13" t="n">
-        <v>0.3341014637211595</v>
+        <v>0.3098095713981506</v>
       </c>
     </row>
     <row r="9">
@@ -2798,7 +2798,7 @@
         </is>
       </c>
       <c r="B17" s="13" t="n">
-        <v>0.3573828894703562</v>
+        <v>0.3155765623218869</v>
       </c>
     </row>
     <row r="18">
@@ -2878,14 +2878,14 @@
         </is>
       </c>
       <c r="B3" s="9" t="n">
-        <v>3.33274603069955</v>
+        <v>4.19372149068249</v>
       </c>
       <c r="C3" s="9" t="n">
-        <v>12.64818881769384</v>
+        <v>14.11260456761903</v>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>return on equity of 16.7% against a cost of equity of 37.1%</t>
+          <t>return on equity of 16.7% against a cost of equity of 32.6%</t>
         </is>
       </c>
     </row>
@@ -2896,10 +2896,10 @@
         </is>
       </c>
       <c r="B4" s="9" t="n">
-        <v>15.46564175092172</v>
+        <v>18.57572105502225</v>
       </c>
       <c r="C4" s="9" t="n">
-        <v>23.80326205675117</v>
+        <v>27.421482628649</v>
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>

--- a/engine/publish_queue/TMGH/TMGH_Valuation_Model_10092026.xlsx
+++ b/engine/publish_queue/TMGH/TMGH_Valuation_Model_10092026.xlsx
@@ -33,7 +33,7 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="2">
     <numFmt numFmtId="164" formatCode="0.0%"/>
-    <numFmt numFmtId="165" formatCode="0.0000"/>
+    <numFmt numFmtId="165" formatCode="0.000000"/>
   </numFmts>
   <fonts count="6">
     <font>
@@ -507,7 +507,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Egyptian Exchange · TMGH · Egyptian pounds · 2026-09-02</t>
+          <t>Egyptian Exchange · TMGH · Egyptian pounds · 2026-09-10</t>
         </is>
       </c>
     </row>
@@ -3346,7 +3346,7 @@
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">  reference: minority at book</t>
+          <t xml:space="preserve">  reference: minority at book — NOT deducted below</t>
         </is>
       </c>
       <c r="B13" s="7" t="n">
@@ -3360,7 +3360,7 @@
         </is>
       </c>
       <c r="B14" s="17">
-        <f>B11+B13</f>
+        <f>B11+B12</f>
         <v/>
       </c>
     </row>
@@ -3897,7 +3897,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K15"/>
+  <dimension ref="A1:K16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -4232,136 +4232,173 @@
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
+          <t>Cost of capital, this year's forward rate</t>
+        </is>
+      </c>
+      <c r="B9" s="15" t="n">
+        <v>0.3155765623218869</v>
+      </c>
+      <c r="C9" s="15" t="n">
+        <v>0.2702845796487516</v>
+      </c>
+      <c r="D9" s="15" t="n">
+        <v>0.2340509935102434</v>
+      </c>
+      <c r="E9" s="15" t="n">
+        <v>0.2068758039063623</v>
+      </c>
+      <c r="F9" s="15" t="n">
+        <v>0.1887590108371082</v>
+      </c>
+      <c r="G9" s="15" t="n">
+        <v>0.1887590108371082</v>
+      </c>
+      <c r="H9" s="15" t="n">
+        <v>0.1887590108371082</v>
+      </c>
+      <c r="I9" s="15" t="n">
+        <v>0.1887590108371082</v>
+      </c>
+      <c r="J9" s="15" t="n">
+        <v>0.1887590108371082</v>
+      </c>
+      <c r="K9" s="15" t="n">
+        <v>0.1887590108371082</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
           <t>Discount factor</t>
         </is>
       </c>
-      <c r="B9" s="19">
-        <f>1/(1+'Summary'!$B$14)^1</f>
-        <v/>
-      </c>
-      <c r="C9" s="19">
-        <f>1/(1+'Summary'!$B$14)^2</f>
-        <v/>
-      </c>
-      <c r="D9" s="19">
-        <f>1/(1+'Summary'!$B$14)^3</f>
-        <v/>
-      </c>
-      <c r="E9" s="19">
-        <f>1/(1+'Summary'!$B$14)^4</f>
-        <v/>
-      </c>
-      <c r="F9" s="19">
-        <f>1/(1+'Summary'!$B$14)^5</f>
-        <v/>
-      </c>
-      <c r="G9" s="19">
-        <f>1/(1+'Summary'!$B$14)^6</f>
-        <v/>
-      </c>
-      <c r="H9" s="19">
-        <f>1/(1+'Summary'!$B$14)^7</f>
-        <v/>
-      </c>
-      <c r="I9" s="19">
-        <f>1/(1+'Summary'!$B$14)^8</f>
-        <v/>
-      </c>
-      <c r="J9" s="19">
-        <f>1/(1+'Summary'!$B$14)^9</f>
-        <v/>
-      </c>
-      <c r="K9" s="19">
-        <f>1/(1+'Summary'!$B$14)^10</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="11" t="inlineStr">
+      <c r="B10" s="19">
+        <f>1/(1+B9)</f>
+        <v/>
+      </c>
+      <c r="C10" s="19">
+        <f>B10/(1+C9)</f>
+        <v/>
+      </c>
+      <c r="D10" s="19">
+        <f>C10/(1+D9)</f>
+        <v/>
+      </c>
+      <c r="E10" s="19">
+        <f>D10/(1+E9)</f>
+        <v/>
+      </c>
+      <c r="F10" s="19">
+        <f>E10/(1+F9)</f>
+        <v/>
+      </c>
+      <c r="G10" s="19">
+        <f>F10/(1+G9)</f>
+        <v/>
+      </c>
+      <c r="H10" s="19">
+        <f>G10/(1+H9)</f>
+        <v/>
+      </c>
+      <c r="I10" s="19">
+        <f>H10/(1+I9)</f>
+        <v/>
+      </c>
+      <c r="J10" s="19">
+        <f>I10/(1+J9)</f>
+        <v/>
+      </c>
+      <c r="K10" s="19">
+        <f>J10/(1+K9)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="11" t="inlineStr">
         <is>
           <t>Present value</t>
         </is>
       </c>
-      <c r="B10" s="8">
-        <f>B8*B9</f>
-        <v/>
-      </c>
-      <c r="C10" s="8">
-        <f>C8*C9</f>
-        <v/>
-      </c>
-      <c r="D10" s="8">
-        <f>D8*D9</f>
-        <v/>
-      </c>
-      <c r="E10" s="8">
-        <f>E8*E9</f>
-        <v/>
-      </c>
-      <c r="F10" s="8">
-        <f>F8*F9</f>
-        <v/>
-      </c>
-      <c r="G10" s="8">
-        <f>G8*G9</f>
-        <v/>
-      </c>
-      <c r="H10" s="8">
-        <f>H8*H9</f>
-        <v/>
-      </c>
-      <c r="I10" s="8">
-        <f>I8*I9</f>
-        <v/>
-      </c>
-      <c r="J10" s="8">
-        <f>J8*J9</f>
-        <v/>
-      </c>
-      <c r="K10" s="8">
-        <f>K8*K9</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="11" t="inlineStr">
+      <c r="B11" s="8">
+        <f>B8*B10</f>
+        <v/>
+      </c>
+      <c r="C11" s="8">
+        <f>C8*C10</f>
+        <v/>
+      </c>
+      <c r="D11" s="8">
+        <f>D8*D10</f>
+        <v/>
+      </c>
+      <c r="E11" s="8">
+        <f>E8*E10</f>
+        <v/>
+      </c>
+      <c r="F11" s="8">
+        <f>F8*F10</f>
+        <v/>
+      </c>
+      <c r="G11" s="8">
+        <f>G8*G10</f>
+        <v/>
+      </c>
+      <c r="H11" s="8">
+        <f>H8*H10</f>
+        <v/>
+      </c>
+      <c r="I11" s="8">
+        <f>I8*I10</f>
+        <v/>
+      </c>
+      <c r="J11" s="8">
+        <f>J8*J10</f>
+        <v/>
+      </c>
+      <c r="K11" s="8">
+        <f>K8*K10</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="11" t="inlineStr">
         <is>
           <t>Sum of the explicit years</t>
         </is>
       </c>
-      <c r="B12" s="17">
-        <f>SUM(B10:K10)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="4" t="inlineStr">
-        <is>
-          <t>Order book still unconverted, present value</t>
-        </is>
-      </c>
-      <c r="B13" s="7" t="n">
-        <v>20701.71014497908</v>
+      <c r="B13" s="17">
+        <f>SUM(B11:K11)</f>
+        <v/>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
+          <t>Order book still unconverted, present value</t>
+        </is>
+      </c>
+      <c r="B14" s="7" t="n">
+        <v>20701.71014497908</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
           <t>Recurring businesses beyond the window, present value</t>
         </is>
       </c>
-      <c r="B14" s="7" t="n">
+      <c r="B15" s="7" t="n">
         <v>39398.8589185091</v>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="11" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="11" t="inlineStr">
         <is>
           <t>Enterprise value</t>
         </is>
       </c>
-      <c r="B15" s="17">
-        <f>B12+B13+B14</f>
+      <c r="B16" s="17">
+        <f>B13+B14+B15</f>
         <v/>
       </c>
     </row>
